--- a/output/final/geo/geo distributors (status checked)/status_check_report.xlsx
+++ b/output/final/geo/geo distributors (status checked)/status_check_report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status changes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Status changes'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -636,93 +636,93 @@
     <row r="4" ht="33" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>geo_ag_drone_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Gurudrone Agritech Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>gurudrone.com</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Gurudrone Agritech Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="33" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
           <t>geo_ai_geospatial_verified_distributors</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Elcome Technologies Private Limited</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>http://elcometech.com</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Hexagon</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Hexagon acquired all outstanding shares of Elcome Technologies Pvt. Ltd. in 2007, according to an official Hexagon press release.</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>renamed</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>geo_ai_geospatial_verified_distributors</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>DesignTech Systems Private Limited</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://www.designtechproducts.com</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Same company as 'DesignTech Systems' (same website and country, or same name and city) - listed once.</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>geo_ai_geospatial_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Geosys Enterprise Solutions Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>geosys.co.in</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -734,7 +734,7 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Geosys Enterprise Solutions Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'DesignTech Systems' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Altitud Digitals India Pvt. LTD</t>
+          <t>Geosys Enterprise Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>altitud.co.in</t>
+          <t>geosys.co.in</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -768,7 +768,7 @@
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Altitud Digitals India Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Geosys Enterprise Solutions Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>UDC India</t>
+          <t>Altitud Digitals India Pvt. LTD</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>https://udcindia.in</t>
+          <t>altitud.co.in</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'UDC India Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Altitud Digitals India Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -814,42 +814,34 @@
     <row r="9" ht="33" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>geo_commercial_drone_services_verified_distributors</t>
+          <t>geo_ai_geospatial_verified_distributors</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Scandron</t>
+          <t>UDC India</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>https://scandron.com</t>
+          <t>https://udcindia.in</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Magellanic Cloud acquired a 70% majority stake in drone manufacturer Scandron in March 2023, according to a report by Business Standard.</t>
+          <t>Same company as 'UDC India Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
@@ -861,12 +853,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Asteria Aerospace Limited (acquired by Reliance Industries Limited)</t>
+          <t>Scandron</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>https://www.asteria.co.in</t>
+          <t>https://scandron.com</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -876,17 +868,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Reliance Industries Limited</t>
+          <t>Magellanic Cloud</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Reliance Industries acquired a majority stake in Asteria Aerospace through its subsidiary in December 2019, according to a report by Moneycontrol.</t>
+          <t>Magellanic Cloud acquired a 70% majority stake in drone manufacturer Scandron in March 2023, according to a report by Business Standard.</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -903,37 +895,37 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>DronaMaps Private Limited (acquired by AiDash)</t>
+          <t>Asteria Aerospace Limited (acquired by Reliance Industries Limited)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>https://dronamaps.com</t>
+          <t>https://www.asteria.co.in</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>AiDash</t>
+          <t>Reliance Industries Limited</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>DronaMaps was acquired by AiDash in 2022 according to eChai Ventures.</t>
+          <t>Reliance Industries acquired a majority stake in Asteria Aerospace through its subsidiary in December 2019, according to a report by Moneycontrol.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -945,37 +937,37 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Geokno India Private Limited</t>
+          <t>DronaMaps Private Limited (acquired by AiDash)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>geokno.com</t>
+          <t>https://dronamaps.com</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>GMR Group</t>
+          <t>AiDash</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>GMR Group acquired a majority stake in Geokno in 2012 according to the company's profile on PitchBook.</t>
+          <t>DronaMaps was acquired by AiDash in 2022 according to eChai Ventures.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -987,12 +979,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Dhaksha Unmanned Systems Private Limited</t>
+          <t>Geokno India Private Limited</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>dhakshadrones.com</t>
+          <t>geokno.com</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1002,17 +994,17 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Coromandel International</t>
+          <t>GMR Group</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Coromandel International acquired a majority 51% stake in Dhaksha Unmanned Systems Private Limited in June 2023, according to The Times of India.</t>
+          <t>GMR Group acquired a majority stake in Geokno in 2012 according to the company's profile on PitchBook.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1029,29 +1021,37 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Skylark Drones Private Limited</t>
+          <t>Dhaksha Unmanned Systems Private Limited</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>https://skylarkdrones.com</t>
+          <t>dhakshadrones.com</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Coromandel International</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Skylark Drones' (same website and country, or same name and city) - listed once.</t>
+          <t>Coromandel International acquired a majority 51% stake in Dhaksha Unmanned Systems Private Limited in June 2023, according to The Times of India.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Garuda Aerospace</t>
+          <t>Skylark Drones Private Limited</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>garudaaerospace.com</t>
+          <t>https://skylarkdrones.com</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="F15" s="9" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Garuda Aerospace Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Skylark Drones' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Schnell Drone Technologies Limited</t>
+          <t>Garuda Aerospace</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>schnellinformatics.com</t>
+          <t>garudaaerospace.com</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Schnell Drone Technologies Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Garuda Aerospace Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Tripathi Aerospace Pvt Ltd</t>
+          <t>Schnell Drone Technologies Limited</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/company/tripathi-aerospace-private-limited</t>
+          <t>schnellinformatics.com</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1148,7 +1148,7 @@
       <c r="F17" s="9" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Vayu Drone Technologies Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Schnell Drone Technologies Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -1160,84 +1160,68 @@
     <row r="18" ht="33" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>geo_digital_twin_verified_distributors</t>
+          <t>geo_commercial_drone_services_verified_distributors</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Capricot Technologies Private Limited (acquired by ARKANCE)</t>
+          <t>Vayu Drone Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>capricot.com</t>
+          <t>linkedin.com</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>ARKANCE</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Capricot Technologies was acquired by ARKANCE in June 2023 and rebranded entirely to ARKANCE IN Private Limited in August 2024 according to PR Newswire.</t>
+          <t>Same company as 'Vayu Drone Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>geo_digital_twin_verified_distributors</t>
+          <t>geo_commercial_drone_services_verified_distributors</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Embee Software Pvt. Ltd (acquired by Noventiq)</t>
+          <t>Tripathi Aerospace Pvt Ltd</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>embee.co.in</t>
+          <t>https://in.linkedin.com/company/tripathi-aerospace-private-limited</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Noventiq</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Noventiq acquired a majority stake in Embee Software Private Limited in 2021, according to an ICRA rating report.</t>
+          <t>Same company as 'Vayu Drone Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
@@ -1249,29 +1233,37 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>USAM Technology Solutions Private Limited</t>
+          <t>Capricot Technologies Private Limited (acquired by ARKANCE)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>usamcad.in</t>
+          <t>capricot.com</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ARKANCE</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'USAM Technology Solutions Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Capricot Technologies was acquired by ARKANCE in June 2023 and rebranded entirely to ARKANCE IN Private Limited in August 2024 according to PR Newswire.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -1283,29 +1275,37 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Ram Caddsys Pvt Ltd</t>
+          <t>Embee Software Pvt. Ltd (acquired by Noventiq)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>ramcaddsys.com</t>
+          <t>embee.co.in</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Noventiq</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'RAM CADDSYS PRIVATE LIMITED' (same website and country, or same name and city) - listed once.</t>
+          <t>Noventiq acquired a majority stake in Embee Software Private Limited in 2021, according to an ICRA rating report.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Accutech Technologies Private Limited</t>
+          <t>USAM Technology Solutions Private Limited</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>https://accutechindia.in</t>
+          <t>usamcad.in</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1334,7 +1334,7 @@
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Accutech Technologies Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'USAM Technology Solutions Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Softdesk Technologies</t>
+          <t>Ram Caddsys Pvt Ltd</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>softdesktechnologies.com</t>
+          <t>ramcaddsys.com</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="F23" s="9" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Softdesk Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'RAM CADDSYS PRIVATE LIMITED' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -1380,84 +1380,68 @@
     <row r="24" ht="33" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>geo_drone_infra_inspection_verified_distributors</t>
+          <t>geo_digital_twin_verified_distributors</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Asteria Aerospace</t>
+          <t>Accutech Technologies Private Limited</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>https://www.asteria.co.in</t>
+          <t>https://accutechindia.in</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Reliance Industries</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reliance Industries acquired a majority stake in Asteria Aerospace in December 2019.</t>
+          <t>Same company as 'Accutech Technologies Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>geo_drone_infra_inspection_verified_distributors</t>
+          <t>geo_digital_twin_verified_distributors</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Scandron</t>
+          <t>Softdesk Technologies</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>https://www.scandron.com</t>
+          <t>softdesktechnologies.com</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Magellanic Cloud acquired a 70% majority stake in drone manufacturer Scandron in March 2023, according to a report by Business Standard.</t>
+          <t>Same company as 'Softdesk Technologies Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
@@ -1469,37 +1453,37 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>AirProbe</t>
+          <t>Asteria Aerospace</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>https://airprobe.tech</t>
+          <t>https://www.asteria.co.in</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DroneBase</t>
+          <t>Reliance Industries</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>AirProbe was acquired by DroneBase in January 2022 as reported by YourStory.</t>
+          <t>Reliance Industries acquired a majority stake in Asteria Aerospace in December 2019.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1495,12 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Geokno India Private Limited</t>
+          <t>Scandron</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>https://geokno.com</t>
+          <t>https://www.scandron.com</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1526,17 +1510,17 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>GMR Group</t>
+          <t>Magellanic Cloud</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>GMR Group acquired a majority stake in Geokno in 2012 according to the company's profile on PitchBook.</t>
+          <t>Magellanic Cloud acquired a 70% majority stake in drone manufacturer Scandron in March 2023, according to a report by Business Standard.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -1548,93 +1532,101 @@
     <row r="28" ht="33" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>geo_drone_survey_lidar_verified_distributors</t>
+          <t>geo_drone_infra_inspection_verified_distributors</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Elcome Technologies Private Limited</t>
+          <t>AirProbe</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>elcometech.com</t>
+          <t>https://airprobe.tech</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Hexagon</t>
+          <t>DroneBase</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Hexagon acquired all outstanding shares of Elcome Technologies Pvt. Ltd. in 2007, according to an official Hexagon press release.</t>
+          <t>AirProbe was acquired by DroneBase in January 2022 as reported by YourStory.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>geo_drone_survey_lidar_verified_distributors</t>
+          <t>geo_drone_infra_inspection_verified_distributors</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Elcome Technologies Pvt. Ltd.</t>
+          <t>Geokno India Private Limited</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>elcome.in</t>
+          <t>https://geokno.com</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="9" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>GMR Group</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Elcome Technologies Private Limited (acquired by Hexagon)' (same website and country, or same name and city) - listed once.</t>
+          <t>GMR Group acquired a majority stake in Geokno in 2012 according to the company's profile on PitchBook.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>geo_drone_survey_lidar_verified_distributors</t>
+          <t>geo_drone_infra_inspection_verified_distributors</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Skipper Technologies India Pvt. Ltd.</t>
+          <t>Snesar Aerial Intelligence</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>skippertech.com</t>
+          <t>snesar.com</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1646,7 +1638,7 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Skipper Technologies India Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Snesar Aerial Intelligence Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1663,29 +1655,37 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Divine Empire India Pvt. Ltd.</t>
+          <t>Elcome Technologies Private Limited</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>thedivineempire.org</t>
+          <t>elcometech.com</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Hexagon</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Divine Empire India Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Hexagon acquired all outstanding shares of Elcome Technologies Pvt. Ltd. in 2007, according to an official Hexagon press release.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>RCHobbytech Solutions Private Limited</t>
+          <t>Elcome Technologies Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>rchobbytech.in</t>
+          <t>elcome.in</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'R C Hobby Tech Solutions Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Elcome Technologies Private Limited (acquired by Hexagon)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1726,101 +1726,85 @@
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>geo_gis_analytics_verified_distributors</t>
+          <t>geo_drone_survey_lidar_verified_distributors</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Capricot Technologies Private Limited</t>
+          <t>PCI Software Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>capricot.com</t>
+          <t>pcisoftware.in</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ARKANCE</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Capricot Technologies was acquired by ARKANCE in 2023 and officially renamed to ARKANCE IN Private Limited in 2024, as reported by global press releases and brand integration announcements.</t>
+          <t>Same company as 'PCI Software Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>geo_gis_analytics_verified_distributors</t>
+          <t>geo_drone_survey_lidar_verified_distributors</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ADCC Infocom Pvt. Ltd. (acquired by Ceinsys Tech Limited)</t>
+          <t>Skipper Technologies India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>repl.global</t>
+          <t>skippertech.com</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Ceinsys Tech Limited</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ADCC Infocom Private Limited operates as a wholly owned active subsidiary of Ceinsys Tech Limited (formerly ADCC Infocad), which completed the acquisition process as reported by CARE Ratings.</t>
+          <t>Same company as 'Skipper Technologies India Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>geo_gis_analytics_verified_distributors</t>
+          <t>geo_drone_survey_lidar_verified_distributors</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Tricad Design Consultants Private Limited</t>
+          <t>Divine Empire India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>tricaddesign.com</t>
+          <t>thedivineempire.org</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -1832,7 +1816,7 @@
       <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'TriCAD Design Consultants Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Divine Empire India Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -1844,17 +1828,17 @@
     <row r="36" ht="33" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>geo_gis_analytics_verified_distributors</t>
+          <t>geo_drone_survey_lidar_verified_distributors</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Emitech Infosystems Pvt Ltd</t>
+          <t>RCHobbytech Solutions Private Limited</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>electrical-measuring.com</t>
+          <t>rchobbytech.in</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1866,7 +1850,7 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Emitech Infosystems Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'R C Hobby Tech Solutions Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -1883,29 +1867,37 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Emitech Infosystems Pvt. Ltd.</t>
+          <t>Capricot Technologies Private Limited</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>emitechinfosystems.com</t>
+          <t>capricot.com</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr"/>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ARKANCE</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Emitech Infosystems Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Capricot Technologies was acquired by ARKANCE in 2023 and officially renamed to ARKANCE IN Private Limited in 2024, as reported by global press releases and brand integration announcements.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -1917,214 +1909,190 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Thematic Gis Technology Pvt Ltd</t>
+          <t>ADCC Infocom Pvt. Ltd. (acquired by Ceinsys Tech Limited)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>thematicgis.com</t>
+          <t>repl.global</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Ceinsys Tech Limited</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Thematic GIS Technology Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>ADCC Infocom Private Limited operates as a wholly owned active subsidiary of Ceinsys Tech Limited (formerly ADCC Infocad), which completed the acquisition process as reported by CARE Ratings.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>geo_powerline_utility_drone_verified_distributors</t>
+          <t>geo_gis_analytics_verified_distributors</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>GarudaUAV Soft Solutions Private Limited (acquired by Trentar)</t>
+          <t>Tricad Design Consultants Private Limited</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>https://garudauav.com</t>
+          <t>tricaddesign.com</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Trentar</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>GarudaUAV Soft Solutions Private Limited remains active after a majority stake was acquired by Trentar Private Limited in July 2021, according to an ICRA rating report.</t>
+          <t>Same company as 'TriCAD Design Consultants Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>geo_powerline_utility_drone_verified_distributors</t>
+          <t>geo_gis_analytics_verified_distributors</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Asteria Aerospace (acquired by Reliance Industries)</t>
+          <t>Emitech Infosystems Pvt Ltd</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>asteria.co.in</t>
+          <t>electrical-measuring.com</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Reliance Industries</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Reliance Strategic Business Ventures Limited acquired a majority stake in Asteria Aerospace on 13 December 2019, according to a company announcement.</t>
+          <t>Same company as 'Emitech Infosystems Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>geo_powerline_utility_drone_verified_distributors</t>
+          <t>geo_gis_analytics_verified_distributors</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Throttle Aerospace Systems Pvt. Ltd. (acquired by NeoSky India Limited)</t>
+          <t>Emitech Infosystems Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>throttle.aero</t>
+          <t>emitechinfosystems.com</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>NeoSky India Limited</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="9" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>NeoSky India Limited, a subsidiary of RattanIndia Enterprises, acquired a 60% controlling stake in Throttle Aerospace Systems Private Limited in May 2022, though the company continues to operate under its own name.</t>
+          <t>Same company as 'Emitech Infosystems Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>geo_powerline_utility_drone_verified_distributors</t>
+          <t>geo_gis_analytics_verified_distributors</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Scandron Private Limited</t>
+          <t>Thematic Gis Technology Pvt Ltd</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>scandron.ai</t>
+          <t>thematicgis.com</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud Limited acquired a majority 70% stake in Scandron Private Limited on March 17, 2023, as reported by Business Standard.</t>
+          <t>Same company as 'Thematic GIS Technology Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>geo_telecom_tower_inspection_verified_distributors</t>
+          <t>geo_powerline_utility_drone_verified_distributors</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Asteria Aerospace</t>
+          <t>GarudaUAV Soft Solutions Private Limited (acquired by Trentar)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>https://www.asteria.co.in</t>
+          <t>https://garudauav.com</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2134,17 +2102,17 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Reliance Industries</t>
+          <t>Trentar</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Reliance Industries acquired a majority stake in Asteria Aerospace in December 2019.</t>
+          <t>GarudaUAV Soft Solutions Private Limited remains active after a majority stake was acquired by Trentar Private Limited in July 2021, according to an ICRA rating report.</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -2156,17 +2124,17 @@
     <row r="44" ht="33" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>geo_telecom_tower_inspection_verified_distributors</t>
+          <t>geo_powerline_utility_drone_verified_distributors</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Scandron Private Limited</t>
+          <t>Asteria Aerospace (acquired by Reliance Industries)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>scandron.ai</t>
+          <t>asteria.co.in</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2176,17 +2144,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud</t>
+          <t>Reliance Industries</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud Limited acquired a majority 70% stake in Scandron Private Limited on March 17, 2023, as reported by Business Standard.</t>
+          <t>Reliance Strategic Business Ventures Limited acquired a majority stake in Asteria Aerospace on 13 December 2019, according to a company announcement.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2198,17 +2166,17 @@
     <row r="45" ht="33" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>geo_telecom_tower_inspection_verified_distributors</t>
+          <t>geo_powerline_utility_drone_verified_distributors</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Centillion Networks Private Limited (acquired by Osmose Utilities Services, Inc.)</t>
+          <t>Throttle Aerospace Systems Pvt. Ltd. (acquired by NeoSky India Limited)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>centillionnetworks.com</t>
+          <t>throttle.aero</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2218,17 +2186,17 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Osmose Utilities Services, Inc.</t>
+          <t>NeoSky India Limited</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Centillion Networks Private Limited was acquired by Osmose Utilities Services, Inc. in October 2025, according to the official website statement.</t>
+          <t>NeoSky India Limited, a subsidiary of RattanIndia Enterprises, acquired a 60% controlling stake in Throttle Aerospace Systems Private Limited in May 2022, though the company continues to operate under its own name.</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -2240,80 +2208,76 @@
     <row r="46" ht="33" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>geo_telecom_tower_inspection_verified_distributors</t>
+          <t>geo_powerline_utility_drone_verified_distributors</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Towervision India Pvt Ltd (acquired by Ascend Telecom Infrastructure Private Limited)</t>
+          <t>Scandron Private Limited</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>tower-vision.com</t>
+          <t>scandron.ai</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Ascend Telecom Infrastructure Private Limited</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr"/>
+          <t>Magellanic Cloud</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>The company website states that Tower Vision India Private Limited has been merged with Ascend Telecom Infrastructure Private Limited.</t>
+          <t>Magellanic Cloud Limited acquired a majority 70% stake in Scandron Private Limited on March 17, 2023, as reported by Business Standard.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
     <row r="47" ht="33" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>geo_telecom_tower_inspection_verified_distributors</t>
+          <t>geo_powerline_utility_drone_verified_distributors</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>MobileComm Technologies India Private Limited</t>
+          <t>Magic Myna Private Limited</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>mcpsinc.com</t>
+          <t>https://magicmyna.com</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>UST</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>UST acquired MobileComm on August 29, 2023, fully integrating the telecom engineering firm into its operations as reported by UST Newsroom.</t>
+          <t>Same company as 'Magic Myna' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2289,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Stesalit Systems Limited</t>
+          <t>Asteria Aerospace</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>https://stesalitsystems.com</t>
+          <t>https://www.asteria.co.in</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2340,13 +2304,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Trentar Group</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr"/>
+          <t>Reliance Industries</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>According to the company's website, Stesalit Systems Limited is part of the Trentar Group.</t>
+          <t>Reliance Industries acquired a majority stake in Asteria Aerospace in December 2019.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2363,29 +2331,37 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Toshniwal Enterprises Controls Limited</t>
+          <t>Scandron Private Limited</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>toshniwalcontrols.com</t>
+          <t>scandron.ai</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="9" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>The company is officially confirmed as under liquidation according to ministry data sourced via ZaubaCorp.</t>
+          <t>Magellanic Cloud Limited acquired a majority 70% stake in Scandron Private Limited on March 17, 2023, as reported by Business Standard.</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2397,33 +2373,37 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Zeppelin Mobile Systems India Ltd.</t>
+          <t>Centillion Networks Private Limited (acquired by Osmose Utilities Services, Inc.)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>zeppelin-india.com</t>
+          <t>centillionnetworks.com</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Osmose Utilities Services, Inc.</t>
+        </is>
+      </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The company, which was renamed Zep Infratech Limited, entered liquidation following a March 2021 NCLT order according to documentation on Gem.wiki.</t>
+          <t>Centillion Networks Private Limited was acquired by Osmose Utilities Services, Inc. in October 2025, according to the official website statement.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2435,29 +2415,33 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Dev Krupa Enterprise</t>
+          <t>Towervision India Pvt Ltd (acquired by Ascend Telecom Infrastructure Private Limited)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>://indiamart.com</t>
+          <t>tower-vision.com</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr"/>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Ascend Telecom Infrastructure Private Limited</t>
+        </is>
+      </c>
       <c r="F51" s="9" t="inlineStr"/>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Nilam Enterprises' (same website and country, or same name and city) - listed once.</t>
+          <t>The company website states that Tower Vision India Private Limited has been merged with Ascend Telecom Infrastructure Private Limited.</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2469,29 +2453,37 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Shivam Infocom Pvt. Ltd.</t>
+          <t>MobileComm Technologies India Private Limited</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>shivaminfocom.co.in</t>
+          <t>mcpsinc.com</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Shivam Infocom Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>UST acquired MobileComm on August 29, 2023, fully integrating the telecom engineering firm into its operations as reported by UST Newsroom.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2503,34 +2495,212 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Stesalit Systems Ltd.</t>
+          <t>Stesalit Systems Limited</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>stesalit-inc.com</t>
+          <t>https://stesalitsystems.com</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Trentar Group</t>
+        </is>
+      </c>
       <c r="F53" s="9" t="inlineStr"/>
       <c r="G53" s="6" t="inlineStr">
         <is>
+          <t>According to the company's website, Stesalit Systems Limited is part of the Trentar Group.</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>geo_telecom_tower_inspection_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Toshniwal Enterprises Controls Limited</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>toshniwalcontrols.com</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>The company is officially confirmed as under liquidation according to ministry data sourced via ZaubaCorp.</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>geo_telecom_tower_inspection_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Zeppelin Mobile Systems India Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>zeppelin-india.com</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>The company, which was renamed Zep Infratech Limited, entered liquidation following a March 2021 NCLT order according to documentation on Gem.wiki.</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>geo_telecom_tower_inspection_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Dev Krupa Enterprise</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>://indiamart.com</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Nilam Enterprises' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>geo_telecom_tower_inspection_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Shivam Infocom Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>shivaminfocom.co.in</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Shivam Infocom Private Limited' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="33" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>geo_telecom_tower_inspection_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Stesalit Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>stesalit-inc.com</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>Same company as 'Stesalit Systems Limited (acquired by Trentar Group)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H53"/>
+  <autoFilter ref="A1:H58"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2584,6 +2754,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
